--- a/月ノルマ/月間週次予定表_2026年9月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年9月版.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9月予定表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="9月予定表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1457,7 +1457,7 @@
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>第5週
-9/28〜10/4
+9/28〜9/30
 (日勤2日 15h)
 院内:9/29(スマートワーキング)・9/30(コア会議)</t>
         </is>
